--- a/gsheet.xlsx
+++ b/gsheet.xlsx
@@ -663,7 +663,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="7">
-        <v>37840</v>
+        <v>37475</v>
       </c>
       <c r="C2" s="8">
         <v>8194846705</v>
